--- a/data/2024/36-teleorman/151790-alexandria/budget_file.xlsx
+++ b/data/2024/36-teleorman/151790-alexandria/budget_file.xlsx
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>30.02 total_2024: parent 4.123,00 != sum(children) 1.103,00 (2 children); 30.02 trim1: parent 1.025,00 != sum(children) 225,00 (2 children); 30.02 trim4: parent 720,00 != sum(children) 100,00 (2 children); 30.02 trim2: parent 1.000,00 != sum(children) 200,00 (2 children); 30.02 est2026: parent 4.210,00 != sum(children) 1.110,00 (2 children); 30.02 est2024: parent 4.210,00 != sum(children) 1.110,00 (2 children); 30.02 trim3: parent 1.378,00 != sum(children) 578,00 (2 children); 30.02 est2027: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
+          <t>30.02 est2024: parent 4.210,00 != sum(children) 1.110,00 (2 children); 30.02 trim3: parent 1.378,00 != sum(children) 578,00 (2 children); 30.02 est2027: parent 4.210,00 != sum(children) 1.110,00 (2 children); 30.02 est2026: parent 4.210,00 != sum(children) 1.110,00 (2 children); 30.02 trim4: parent 720,00 != sum(children) 100,00 (2 children); 30.02 total_2024: parent 4.123,00 != sum(children) 1.103,00 (2 children); 30.02 trim2: parent 1.000,00 != sum(children) 200,00 (2 children); 30.02 trim1: parent 1.025,00 != sum(children) 225,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>43.02 trim3: parent 1.360,00 != sum(children) 60,00 (2 children); 43.02 trim1: parent 1.360,00 != sum(children) 60,00 (2 children); 43.02 trim4: parent 1.215,67 != sum(children) 26,65 (2 children); 43.02 trim2: parent 1.360,00 != sum(children) 60,00 (2 children); 43.02 total_2024: parent 5.295,67 != sum(children) 206,65 (2 children)</t>
+          <t>43.02 trim3: parent 1.360,00 != sum(children) 60,00 (2 children); 43.02 trim4: parent 1.215,67 != sum(children) 26,65 (2 children); 43.02 total_2024: parent 5.295,67 != sum(children) 206,65 (2 children); 43.02 trim2: parent 1.360,00 != sum(children) 60,00 (2 children); 43.02 trim1: parent 1.360,00 != sum(children) 60,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>51.02 trim1: parent 6.878,31 != sum(children) 600,00 (1 children); 51.02 total_2024: parent 14,37 != sum(children) 1.200,15 (1 children); 51.02 trim3: parent 4.556,64 != sum(children) 150,15 (1 children); 51.02 trim2: parent 5.388,83 != sum(children) 450,00 (1 children)</t>
+          <t>51.02 trim3: parent 4.556,64 != sum(children) 150,15 (1 children); 51.02 trim2: parent 5.388,83 != sum(children) 450,00 (1 children); 51.02 trim1: parent 6.878,31 != sum(children) 600,00 (1 children); 51.02 total_2024: parent 14,37 != sum(children) 1.200,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>20.01 total: parent 2.205,00 != sum(children) 40,00 (8 children); 20.01 trim3: parent 457,75 != sum(children) 165,50 (8 children); 20.01 trim1: parent 760,50 != sum(children) 356,00 (8 children); 20.01 trim4: parent 259,95 != sum(children) 99,50 (8 children); 20.01 trim2: parent 726,80 != sum(children) 334,00 (8 children); 20.01 total_2024: parent 6,85 != sum(children) 921,85 (8 children)</t>
+          <t>20.01 trim3: parent 457,75 != sum(children) 165,50 (8 children); 20.01 trim4: parent 259,95 != sum(children) 99,50 (8 children); 20.01 total_2024: parent 6,85 != sum(children) 921,85 (8 children); 20.01 total: parent 2.205,00 != sum(children) 40,00 (8 children); 20.01 trim2: parent 726,80 != sum(children) 334,00 (8 children); 20.01 trim1: parent 760,50 != sum(children) 356,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="Q101" s="4" t="inlineStr">
         <is>
-          <t>20.30 total: parent 595,00 != sum(children) 95,00 (3 children); 20.30 total_2024: parent 2,70 != sum(children) 502,70 (3 children)</t>
+          <t>20.30 total_2024: parent 2,70 != sum(children) 502,70 (3 children); 20.30 total: parent 595,00 != sum(children) 95,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Q127" s="4" t="inlineStr">
         <is>
-          <t>20.01 total: parent 51,00 != sum(children) 15,00 (5 children); 20.01 trim3: parent 5,20 != sum(children) 4,70 (5 children); 20.01 trim1: parent 25,30 != sum(children) 21,30 (5 children); 20.01 trim4: parent 3,20 != sum(children) 2,70 (5 children); 20.01 trim2: parent 17,30 != sum(children) 12,30 (5 children); 20.01 total_2024: parent 0,63 != sum(children) 26,63 (5 children)</t>
+          <t>20.01 trim3: parent 5,20 != sum(children) 4,70 (5 children); 20.01 trim4: parent 3,20 != sum(children) 2,70 (5 children); 20.01 total_2024: parent 0,63 != sum(children) 26,63 (5 children); 20.01 total: parent 51,00 != sum(children) 15,00 (5 children); 20.01 trim2: parent 17,30 != sum(children) 12,30 (5 children); 20.01 trim1: parent 25,30 != sum(children) 21,30 (5 children)</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 20,19 != sum(children) 13,15 (2 children); 61.02 trim3: parent 1.019,66 != sum(children) 983,56 (2 children); 61.02 trim1: parent 1.337,75 != sum(children) 1.256,35 (2 children); 61.02 trim4: parent 859,10 != sum(children) 847,10 (2 children); 61.02 trim2: parent 1.088,03 != sum(children) 1.030,03 (2 children); 61.02 est2026: parent 4.500,00 != sum(children) 4.300,00 (2 children); 61.02 est2024: parent 4.200,00 != sum(children) 4.100,00 (2 children); 61.02 total: parent 4.304,54 != sum(children) 4.117,04 (2 children); 61.02 est2027: parent 4.800,00 != sum(children) 4.500,00 (2 children); 61.02 trim1: parent 1.337,75 != sum(children) 55,50 (1 children); 61.02 total_2024: parent 20,19 != sum(children) 7,04 (1 children); 61.02 total: parent 4.304,54 != sum(children) 55,50 (1 children)</t>
+          <t>61.02 est2024: parent 4.200,00 != sum(children) 4.100,00 (2 children); 61.02 trim3: parent 1.019,66 != sum(children) 983,56 (2 children); 61.02 est2027: parent 4.800,00 != sum(children) 4.500,00 (2 children); 61.02 est2026: parent 4.500,00 != sum(children) 4.300,00 (2 children); 61.02 trim4: parent 859,10 != sum(children) 847,10 (2 children); 61.02 total_2024: parent 20,19 != sum(children) 13,15 (2 children); 61.02 total: parent 4.304,54 != sum(children) 4.117,04 (2 children); 61.02 trim2: parent 1.088,03 != sum(children) 1.030,03 (2 children); 61.02 trim1: parent 1.337,75 != sum(children) 1.256,35 (2 children); 61.02 total_2024: parent 20,19 != sum(children) 7,04 (1 children); 61.02 trim1: parent 1.337,75 != sum(children) 55,50 (1 children); 61.02 total: parent 4.304,54 != sum(children) 55,50 (1 children)</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="Q156" s="4" t="inlineStr">
         <is>
-          <t>10 trim3: parent 879,66 != sum(children) 699,66 (2 children); 10 trim1: parent 980,85 != sum(children) 716,85 (2 children); 10 trim4: parent 818,50 != sum(children) 678,50 (2 children); 10 trim2: parent 890,03 != sum(children) 710,03 (2 children); 10 total_2024: parent 3.569,04 != sum(children) 2.805,04 (2 children)</t>
+          <t>10 trim3: parent 879,66 != sum(children) 699,66 (2 children); 10 trim4: parent 818,50 != sum(children) 678,50 (2 children); 10 total_2024: parent 3.569,04 != sum(children) 2.805,04 (2 children); 10 trim2: parent 890,03 != sum(children) 710,03 (2 children); 10 trim1: parent 980,85 != sum(children) 716,85 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="Q165" s="4" t="inlineStr">
         <is>
-          <t>20.01 total: parent 315,00 != sum(children) 40,00 (9 children); 20.01 total_2024: parent 1,32 != sum(children) 276,32 (9 children)</t>
+          <t>20.01 total_2024: parent 1,32 != sum(children) 276,32 (9 children); 20.01 total: parent 315,00 != sum(children) 40,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="Q196" s="4" t="inlineStr">
         <is>
-          <t>65.02 total: parent 59.801,17 != sum(children) 49.662,47 (5 children); 65.02 total_2024: parent 416,93 != sum(children) 10.555,63 (5 children); 65.02 trim3: parent 17.777,69 != sum(children) 4.214,85 (1 children); 65.02 trim1: parent 19.701,69 != sum(children) 4.303,74 (1 children); 65.02 trim4: parent 3.072,36 != sum(children) 2.150,33 (1 children); 65.02 trim2: parent 19.249,43 != sum(children) 4.286,44 (1 children); 65.02 total: parent 59.801,17 != sum(children) 14.955,36 (1 children)</t>
+          <t>65.02 total_2024: parent 416,93 != sum(children) 10.555,63 (5 children); 65.02 total: parent 59.801,17 != sum(children) 49.662,47 (5 children); 65.02 trim3: parent 17.777,69 != sum(children) 4.214,85 (1 children); 65.02 trim4: parent 3.072,36 != sum(children) 2.150,33 (1 children); 65.02 total: parent 59.801,17 != sum(children) 14.955,36 (1 children); 65.02 trim2: parent 19.249,43 != sum(children) 4.286,44 (1 children); 65.02 trim1: parent 19.701,69 != sum(children) 4.303,74 (1 children)</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="Q227" s="4" t="inlineStr">
         <is>
-          <t>57.02 trim3: parent 274,65 != sum(children) 264,65 (2 children); 57.02 trim1: parent 306,25 != sum(children) 286,25 (2 children); 57.02 trim4: parent 146,57 != sum(children) 143,57 (2 children); 57.02 trim2: parent 305,50 != sum(children) 275,50 (2 children); 57.02 total_2024: parent 1.032,97 != sum(children) 969,97 (2 children)</t>
+          <t>57.02 trim3: parent 274,65 != sum(children) 264,65 (2 children); 57.02 trim4: parent 146,57 != sum(children) 143,57 (2 children); 57.02 total_2024: parent 1.032,97 != sum(children) 969,97 (2 children); 57.02 trim2: parent 305,50 != sum(children) 275,50 (2 children); 57.02 trim1: parent 306,25 != sum(children) 286,25 (2 children)</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="Q257" s="4" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 38,00 != sum(children) 32,00 (7 children); 20.01 trim2: parent 25,00 != sum(children) 23,00 (7 children); 20.01 total_2024: parent 90,00 != sum(children) 82,00 (7 children)</t>
+          <t>20.01 total_2024: parent 90,00 != sum(children) 82,00 (7 children); 20.01 trim2: parent 25,00 != sum(children) 23,00 (7 children); 20.01 trim1: parent 38,00 != sum(children) 32,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="Q276" s="4" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 8.488,90 != sum(children) 349,00 (1 children); 67.02 total_2024: parent 22.298,25 != sum(children) 606,49 (1 children); 67.02 trim3: parent 4.614,89 != sum(children) 57,49 (1 children); 67.02 trim2: parent 8.002,20 != sum(children) 200,00 (1 children)</t>
+          <t>67.02 trim3: parent 4.614,89 != sum(children) 57,49 (1 children); 67.02 trim2: parent 8.002,20 != sum(children) 200,00 (1 children); 67.02 trim1: parent 8.488,90 != sum(children) 349,00 (1 children); 67.02 total_2024: parent 22.298,25 != sum(children) 606,49 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="Q294" s="4" t="inlineStr">
         <is>
-          <t>59 trim3: parent 207,00 != sum(children) 27,00 (4 children); 59 trim2: parent 1.321,00 != sum(children) 1.206,00 (4 children); 59 total_2024: parent 1.670,00 != sum(children) 1.375,00 (4 children)</t>
+          <t>59 trim3: parent 207,00 != sum(children) 27,00 (4 children); 59 total_2024: parent 1.670,00 != sum(children) 1.375,00 (4 children); 59 trim2: parent 1.321,00 != sum(children) 1.206,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="Q322" s="4" t="inlineStr">
         <is>
-          <t>20 trim3: parent 489,00 != sum(children) 459,00 (9 children); 20 trim1: parent 1.439,00 != sum(children) 1.176,00 (9 children); 20 trim2: parent 978,50 != sum(children) 748,50 (9 children); 20 total_2024: parent 3.000,00 != sum(children) 2.477,00 (9 children)</t>
+          <t>20 trim3: parent 489,00 != sum(children) 459,00 (9 children); 20 total_2024: parent 3.000,00 != sum(children) 2.477,00 (9 children); 20 trim2: parent 978,50 != sum(children) 748,50 (9 children); 20 trim1: parent 1.439,00 != sum(children) 1.176,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="Q364" s="4" t="inlineStr">
         <is>
-          <t>70.02 total: parent 155.554,72 != sum(children) 153.854,72 (3 children); 70.02 total_2024: parent 114,80 != sum(children) 1.814,80 (3 children); 70.02 total_2024: parent 114,80 != sum(children) 95,95 (1 children); 70.02 trim3: parent 36.055,60 != sum(children) 700,00 (1 children); 70.02 trim1: parent 47.434,15 != sum(children) 1.957,00 (1 children); 70.02 trim4: parent 26.081,17 != sum(children) 762,30 (1 children); 70.02 trim2: parent 45.983,80 != sum(children) 1.500,00 (1 children); 70.02 total: parent 155.554,72 != sum(children) 4.919,30 (1 children)</t>
+          <t>70.02 total_2024: parent 114,80 != sum(children) 1.814,80 (3 children); 70.02 total: parent 155.554,72 != sum(children) 153.854,72 (3 children); 70.02 trim3: parent 36.055,60 != sum(children) 700,00 (1 children); 70.02 trim4: parent 26.081,17 != sum(children) 762,30 (1 children); 70.02 total_2024: parent 114,80 != sum(children) 95,95 (1 children); 70.02 total: parent 155.554,72 != sum(children) 4.919,30 (1 children); 70.02 trim2: parent 45.983,80 != sum(children) 1.500,00 (1 children); 70.02 trim1: parent 47.434,15 != sum(children) 1.957,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="Q373" s="4" t="inlineStr">
         <is>
-          <t>20 total: parent 5.591,65 != sum(children) 2.741,65 (4 children); 20 total_2024: parent 18,85 != sum(children) 2.868,85 (4 children)</t>
+          <t>20 total_2024: parent 18,85 != sum(children) 2.868,85 (4 children); 20 total: parent 5.591,65 != sum(children) 2.741,65 (4 children)</t>
         </is>
       </c>
     </row>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="Q407" s="4" t="inlineStr">
         <is>
-          <t>20.01 total: parent 9.890,00 != sum(children) 7.890,00 (5 children); 20.01 total_2024: parent 500,51 != sum(children) 2.500,51 (5 children)</t>
+          <t>20.01 total_2024: parent 500,51 != sum(children) 2.500,51 (5 children); 20.01 total: parent 9.890,00 != sum(children) 7.890,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="Q419" s="4" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 2.931,65 != sum(children) 2.274,90 (1 children); 84.02 trim3: parent 26.505,00 != sum(children) 7.000,00 (1 children); 84.02 trim1: parent 52.140,95 != sum(children) 23.179,59 (1 children); 84.02 trim4: parent 12.117,02 != sum(children) 3.946,75 (1 children); 84.02 trim2: parent 35.390,21 != sum(children) 8.000,00 (1 children); 84.02 total: parent 126.153,18 != sum(children) 42.126,34 (1 children)</t>
+          <t>84.02 trim3: parent 26.505,00 != sum(children) 7.000,00 (1 children); 84.02 trim4: parent 12.117,02 != sum(children) 3.946,75 (1 children); 84.02 total_2024: parent 2.931,65 != sum(children) 2.274,90 (1 children); 84.02 total: parent 126.153,18 != sum(children) 42.126,34 (1 children); 84.02 trim2: parent 35.390,21 != sum(children) 8.000,00 (1 children); 84.02 trim1: parent 52.140,95 != sum(children) 23.179,59 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Q439" s="4" t="inlineStr">
         <is>
-          <t>84.02.03 total: parent 126.153,18 != sum(children) 124.668,36 (2 children); 84.02.03 total_2024: parent 2.931,65 != sum(children) 4.416,47 (2 children)</t>
+          <t>84.02.03 total_2024: parent 2.931,65 != sum(children) 4.416,47 (2 children); 84.02.03 total: parent 126.153,18 != sum(children) 124.668,36 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43279,12 +43279,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.02 total_2024: parent 4.123,00 != sum(children) 1.103,00 (2 children)</t>
+          <t>30.02 est2024: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.02 trim1: parent 1.025,00 != sum(children) 225,00 (2 children)</t>
+          <t>30.02 trim3: parent 1.378,00 != sum(children) 578,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43339,12 +43339,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.02 trim4: parent 720,00 != sum(children) 100,00 (2 children)</t>
+          <t>30.02 est2027: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43369,12 +43369,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.02 trim2: parent 1.000,00 != sum(children) 200,00 (2 children)</t>
+          <t>30.02 est2026: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43399,12 +43399,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.02 est2026: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
+          <t>30.02 trim4: parent 720,00 != sum(children) 100,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43429,12 +43429,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.02 est2024: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
+          <t>30.02 total_2024: parent 4.123,00 != sum(children) 1.103,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43459,12 +43459,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.02 trim3: parent 1.378,00 != sum(children) 578,00 (2 children)</t>
+          <t>30.02 trim2: parent 1.000,00 != sum(children) 200,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43489,12 +43489,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.02 est2027: parent 4.210,00 != sum(children) 1.110,00 (2 children)</t>
+          <t>30.02 trim1: parent 1.025,00 != sum(children) 225,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43549,12 +43549,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.02 trim1: parent 1.360,00 != sum(children) 60,00 (2 children)</t>
+          <t>43.02 trim4: parent 1.215,67 != sum(children) 26,65 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43579,12 +43579,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.02 trim4: parent 1.215,67 != sum(children) 26,65 (2 children)</t>
+          <t>43.02 total_2024: parent 5.295,67 != sum(children) 206,65 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43639,12 +43639,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43.02 total_2024: parent 5.295,67 != sum(children) 206,65 (2 children)</t>
+          <t>43.02 trim1: parent 1.360,00 != sum(children) 60,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -43669,12 +43669,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.02 trim1: parent 6.878,31 != sum(children) 600,00 (1 children)</t>
+          <t>51.02 trim3: parent 4.556,64 != sum(children) 150,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -43699,12 +43699,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.02 total_2024: parent 14,37 != sum(children) 1.200,15 (1 children)</t>
+          <t>51.02 trim2: parent 5.388,83 != sum(children) 450,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -43729,12 +43729,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.02 trim3: parent 4.556,64 != sum(children) 150,15 (1 children)</t>
+          <t>51.02 trim1: parent 6.878,31 != sum(children) 600,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -43759,12 +43759,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.02 trim2: parent 5.388,83 != sum(children) 450,00 (1 children)</t>
+          <t>51.02 total_2024: parent 14,37 != sum(children) 1.200,15 (1 children)</t>
         </is>
       </c>
     </row>
@@ -43849,12 +43849,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20.01 total: parent 2.205,00 != sum(children) 40,00 (8 children)</t>
+          <t>20.01 trim3: parent 457,75 != sum(children) 165,50 (8 children)</t>
         </is>
       </c>
     </row>
@@ -43879,12 +43879,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 457,75 != sum(children) 165,50 (8 children)</t>
+          <t>20.01 trim4: parent 259,95 != sum(children) 99,50 (8 children)</t>
         </is>
       </c>
     </row>
@@ -43909,12 +43909,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 760,50 != sum(children) 356,00 (8 children)</t>
+          <t>20.01 total_2024: parent 6,85 != sum(children) 921,85 (8 children)</t>
         </is>
       </c>
     </row>
@@ -43939,12 +43939,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 259,95 != sum(children) 99,50 (8 children)</t>
+          <t>20.01 total: parent 2.205,00 != sum(children) 40,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -43999,12 +43999,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 6,85 != sum(children) 921,85 (8 children)</t>
+          <t>20.01 trim1: parent 760,50 != sum(children) 356,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -44029,12 +44029,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20.30 total: parent 595,00 != sum(children) 95,00 (3 children)</t>
+          <t>20.30 total_2024: parent 2,70 != sum(children) 502,70 (3 children)</t>
         </is>
       </c>
     </row>
@@ -44059,12 +44059,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20.30 total_2024: parent 2,70 != sum(children) 502,70 (3 children)</t>
+          <t>20.30 total: parent 595,00 != sum(children) 95,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -44294,12 +44294,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20.01 total: parent 51,00 != sum(children) 15,00 (5 children)</t>
+          <t>20.01 trim3: parent 5,20 != sum(children) 4,70 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44324,12 +44324,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20.01 trim3: parent 5,20 != sum(children) 4,70 (5 children)</t>
+          <t>20.01 trim4: parent 3,20 != sum(children) 2,70 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44354,12 +44354,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 25,30 != sum(children) 21,30 (5 children)</t>
+          <t>20.01 total_2024: parent 0,63 != sum(children) 26,63 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44384,12 +44384,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20.01 trim4: parent 3,20 != sum(children) 2,70 (5 children)</t>
+          <t>20.01 total: parent 51,00 != sum(children) 15,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44444,12 +44444,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 0,63 != sum(children) 26,63 (5 children)</t>
+          <t>20.01 trim1: parent 25,30 != sum(children) 21,30 (5 children)</t>
         </is>
       </c>
     </row>
@@ -44499,12 +44499,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>est2024</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 20,19 != sum(children) 13,15 (2 children)</t>
+          <t>61.02 est2024: parent 4.200,00 != sum(children) 4.100,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44559,12 +44559,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.02 trim1: parent 1.337,75 != sum(children) 1.256,35 (2 children)</t>
+          <t>61.02 est2027: parent 4.800,00 != sum(children) 4.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44589,12 +44589,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.02 trim4: parent 859,10 != sum(children) 847,10 (2 children)</t>
+          <t>61.02 est2026: parent 4.500,00 != sum(children) 4.300,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44619,12 +44619,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.02 trim2: parent 1.088,03 != sum(children) 1.030,03 (2 children)</t>
+          <t>61.02 trim4: parent 859,10 != sum(children) 847,10 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44649,12 +44649,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>est2026</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.02 est2026: parent 4.500,00 != sum(children) 4.300,00 (2 children)</t>
+          <t>61.02 total_2024: parent 20,19 != sum(children) 13,15 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44679,12 +44679,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>est2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.02 est2024: parent 4.200,00 != sum(children) 4.100,00 (2 children)</t>
+          <t>61.02 total: parent 4.304,54 != sum(children) 4.117,04 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44709,12 +44709,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.02 total: parent 4.304,54 != sum(children) 4.117,04 (2 children)</t>
+          <t>61.02 trim2: parent 1.088,03 != sum(children) 1.030,03 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44739,12 +44739,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.02 est2027: parent 4.800,00 != sum(children) 4.500,00 (2 children)</t>
+          <t>61.02 trim1: parent 1.337,75 != sum(children) 1.256,35 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44769,12 +44769,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.02 trim1: parent 1.337,75 != sum(children) 55,50 (1 children)</t>
+          <t>61.02 total_2024: parent 20,19 != sum(children) 7,04 (1 children)</t>
         </is>
       </c>
     </row>
@@ -44799,12 +44799,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 20,19 != sum(children) 7,04 (1 children)</t>
+          <t>61.02 trim1: parent 1.337,75 != sum(children) 55,50 (1 children)</t>
         </is>
       </c>
     </row>
@@ -44914,12 +44914,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10 trim1: parent 980,85 != sum(children) 716,85 (2 children)</t>
+          <t>10 trim4: parent 818,50 != sum(children) 678,50 (2 children)</t>
         </is>
       </c>
     </row>
@@ -44944,12 +44944,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10 trim4: parent 818,50 != sum(children) 678,50 (2 children)</t>
+          <t>10 total_2024: parent 3.569,04 != sum(children) 2.805,04 (2 children)</t>
         </is>
       </c>
     </row>
@@ -45004,12 +45004,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10 total_2024: parent 3.569,04 != sum(children) 2.805,04 (2 children)</t>
+          <t>10 trim1: parent 980,85 != sum(children) 716,85 (2 children)</t>
         </is>
       </c>
     </row>
@@ -45094,12 +45094,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20.01 total: parent 315,00 != sum(children) 40,00 (9 children)</t>
+          <t>20.01 total_2024: parent 1,32 != sum(children) 276,32 (9 children)</t>
         </is>
       </c>
     </row>
@@ -45124,12 +45124,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 1,32 != sum(children) 276,32 (9 children)</t>
+          <t>20.01 total: parent 315,00 != sum(children) 40,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -45154,12 +45154,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.02 total: parent 59.801,17 != sum(children) 49.662,47 (5 children)</t>
+          <t>65.02 total_2024: parent 416,93 != sum(children) 10.555,63 (5 children)</t>
         </is>
       </c>
     </row>
@@ -45184,12 +45184,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 416,93 != sum(children) 10.555,63 (5 children)</t>
+          <t>65.02 total: parent 59.801,17 != sum(children) 49.662,47 (5 children)</t>
         </is>
       </c>
     </row>
@@ -45244,12 +45244,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>65.02 trim1: parent 19.701,69 != sum(children) 4.303,74 (1 children)</t>
+          <t>65.02 trim4: parent 3.072,36 != sum(children) 2.150,33 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45274,12 +45274,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.02 trim4: parent 3.072,36 != sum(children) 2.150,33 (1 children)</t>
+          <t>65.02 total: parent 59.801,17 != sum(children) 14.955,36 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45334,12 +45334,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.02 total: parent 59.801,17 != sum(children) 14.955,36 (1 children)</t>
+          <t>65.02 trim1: parent 19.701,69 != sum(children) 4.303,74 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45419,12 +45419,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>57.02 trim1: parent 306,25 != sum(children) 286,25 (2 children)</t>
+          <t>57.02 trim4: parent 146,57 != sum(children) 143,57 (2 children)</t>
         </is>
       </c>
     </row>
@@ -45449,12 +45449,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>57.02 trim4: parent 146,57 != sum(children) 143,57 (2 children)</t>
+          <t>57.02 total_2024: parent 1.032,97 != sum(children) 969,97 (2 children)</t>
         </is>
       </c>
     </row>
@@ -45509,12 +45509,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>57.02 total_2024: parent 1.032,97 != sum(children) 969,97 (2 children)</t>
+          <t>57.02 trim1: parent 306,25 != sum(children) 286,25 (2 children)</t>
         </is>
       </c>
     </row>
@@ -45624,12 +45624,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20.01 trim1: parent 38,00 != sum(children) 32,00 (7 children)</t>
+          <t>20.01 total_2024: parent 90,00 != sum(children) 82,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -45684,12 +45684,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 90,00 != sum(children) 82,00 (7 children)</t>
+          <t>20.01 trim1: parent 38,00 != sum(children) 32,00 (7 children)</t>
         </is>
       </c>
     </row>
@@ -45714,12 +45714,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 8.488,90 != sum(children) 349,00 (1 children)</t>
+          <t>67.02 trim3: parent 4.614,89 != sum(children) 57,49 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45744,12 +45744,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>67.02 total_2024: parent 22.298,25 != sum(children) 606,49 (1 children)</t>
+          <t>67.02 trim2: parent 8.002,20 != sum(children) 200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45774,12 +45774,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>67.02 trim3: parent 4.614,89 != sum(children) 57,49 (1 children)</t>
+          <t>67.02 trim1: parent 8.488,90 != sum(children) 349,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45804,12 +45804,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 8.002,20 != sum(children) 200,00 (1 children)</t>
+          <t>67.02 total_2024: parent 22.298,25 != sum(children) 606,49 (1 children)</t>
         </is>
       </c>
     </row>
@@ -45889,12 +45889,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>59 trim2: parent 1.321,00 != sum(children) 1.206,00 (4 children)</t>
+          <t>59 total_2024: parent 1.670,00 != sum(children) 1.375,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -45919,12 +45919,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>59 total_2024: parent 1.670,00 != sum(children) 1.375,00 (4 children)</t>
+          <t>59 trim2: parent 1.321,00 != sum(children) 1.206,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -46004,12 +46004,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>20 trim1: parent 1.439,00 != sum(children) 1.176,00 (9 children)</t>
+          <t>20 total_2024: parent 3.000,00 != sum(children) 2.477,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -46064,12 +46064,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 3.000,00 != sum(children) 2.477,00 (9 children)</t>
+          <t>20 trim1: parent 1.439,00 != sum(children) 1.176,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -46094,12 +46094,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.02 total: parent 155.554,72 != sum(children) 153.854,72 (3 children)</t>
+          <t>70.02 total_2024: parent 114,80 != sum(children) 1.814,80 (3 children)</t>
         </is>
       </c>
     </row>
@@ -46124,12 +46124,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 114,80 != sum(children) 1.814,80 (3 children)</t>
+          <t>70.02 total: parent 155.554,72 != sum(children) 153.854,72 (3 children)</t>
         </is>
       </c>
     </row>
@@ -46154,12 +46154,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 114,80 != sum(children) 95,95 (1 children)</t>
+          <t>70.02 trim3: parent 36.055,60 != sum(children) 700,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46184,12 +46184,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.02 trim3: parent 36.055,60 != sum(children) 700,00 (1 children)</t>
+          <t>70.02 trim4: parent 26.081,17 != sum(children) 762,30 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46214,12 +46214,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.02 trim1: parent 47.434,15 != sum(children) 1.957,00 (1 children)</t>
+          <t>70.02 total_2024: parent 114,80 != sum(children) 95,95 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46244,12 +46244,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.02 trim4: parent 26.081,17 != sum(children) 762,30 (1 children)</t>
+          <t>70.02 total: parent 155.554,72 != sum(children) 4.919,30 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46304,12 +46304,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.02 total: parent 155.554,72 != sum(children) 4.919,30 (1 children)</t>
+          <t>70.02 trim1: parent 47.434,15 != sum(children) 1.957,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46334,12 +46334,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>20 total: parent 5.591,65 != sum(children) 2.741,65 (4 children)</t>
+          <t>20 total_2024: parent 18,85 != sum(children) 2.868,85 (4 children)</t>
         </is>
       </c>
     </row>
@@ -46364,12 +46364,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>20 total_2024: parent 18,85 != sum(children) 2.868,85 (4 children)</t>
+          <t>20 total: parent 5.591,65 != sum(children) 2.741,65 (4 children)</t>
         </is>
       </c>
     </row>
@@ -46479,12 +46479,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>20.01 total: parent 9.890,00 != sum(children) 7.890,00 (5 children)</t>
+          <t>20.01 total_2024: parent 500,51 != sum(children) 2.500,51 (5 children)</t>
         </is>
       </c>
     </row>
@@ -46509,12 +46509,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>20.01 total_2024: parent 500,51 != sum(children) 2.500,51 (5 children)</t>
+          <t>20.01 total: parent 9.890,00 != sum(children) 7.890,00 (5 children)</t>
         </is>
       </c>
     </row>
@@ -46539,12 +46539,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 2.931,65 != sum(children) 2.274,90 (1 children)</t>
+          <t>84.02 trim3: parent 26.505,00 != sum(children) 7.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>84.02 trim3: parent 26.505,00 != sum(children) 7.000,00 (1 children)</t>
+          <t>84.02 trim4: parent 12.117,02 != sum(children) 3.946,75 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46599,12 +46599,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>84.02 trim1: parent 52.140,95 != sum(children) 23.179,59 (1 children)</t>
+          <t>84.02 total_2024: parent 2.931,65 != sum(children) 2.274,90 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46629,12 +46629,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>84.02 trim4: parent 12.117,02 != sum(children) 3.946,75 (1 children)</t>
+          <t>84.02 total: parent 126.153,18 != sum(children) 42.126,34 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46689,12 +46689,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>84.02 total: parent 126.153,18 != sum(children) 42.126,34 (1 children)</t>
+          <t>84.02 trim1: parent 52.140,95 != sum(children) 23.179,59 (1 children)</t>
         </is>
       </c>
     </row>
@@ -46744,12 +46744,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>84.02.03 total: parent 126.153,18 != sum(children) 124.668,36 (2 children)</t>
+          <t>84.02.03 total_2024: parent 2.931,65 != sum(children) 4.416,47 (2 children)</t>
         </is>
       </c>
     </row>
@@ -46774,12 +46774,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>84.02.03 total_2024: parent 2.931,65 != sum(children) 4.416,47 (2 children)</t>
+          <t>84.02.03 total: parent 126.153,18 != sum(children) 124.668,36 (2 children)</t>
         </is>
       </c>
     </row>
@@ -47019,7 +47019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -47045,7 +47045,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -47145,27 +47145,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Pagini asteptate</t>
+          <t>Linii anexe separate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Pagini selectate</t>
+          <t>Celule numerice anexe separate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Pagini procesate</t>
+          <t>Pagini asteptate</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -47175,115 +47175,111 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDF complet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
+          <t>Pagini procesate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>827</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>% curat</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>94.90000000000001</v>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>110</v>
+        <v>827</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>% curat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Informatii</t>
+          <t>Erori</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Schema publicare</t>
+          <t>Avertismente</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Bundle conversie</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>bce055ad83aaa9ff53f049a8</t>
-        </is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 sursa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>550a814adb632d3d3e59636827fccae57a818cf6868a2265d3b34377f027cc98</t>
-        </is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Format sursa</t>
+          <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>e67cf056d621cddac53f1d25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 PDF sursa</t>
+          <t>SHA-256 sursa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -47295,10 +47291,34 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Format sursa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>550a814adb632d3d3e59636827fccae57a818cf6868a2265d3b34377f027cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>local, pag. 1-30, 880 linii</t>
         </is>
